--- a/Poseydon_telemetry.xlsx
+++ b/Poseydon_telemetry.xlsx
@@ -1,61 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladi\PycharmProjects\zakl_nto_eto_pizda\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25450BAF-4EF6-43CA-898B-6BE524FCDBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
-  <si>
-    <t>№ измерения</t>
-  </si>
-  <si>
-    <t>ТМ</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Крен</t>
-  </si>
-  <si>
-    <t>Тангаж</t>
-  </si>
-  <si>
-    <t>Рысканье</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -74,25 +46,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -358,43 +389,439 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col width="13.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№ измерения</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ТМ</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Крен</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Тангаж</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Рысканье</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Крен</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Тангаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>-0.5877294004256933</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Poseydon_telemetry.xlsx
+++ b/Poseydon_telemetry.xlsx
@@ -1,61 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladi\PycharmProjects\zakl_nto_eto_pizda\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E482233-6E7D-4407-BEDD-EF439CAEA803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
-  <si>
-    <t>№ измерения</t>
-  </si>
-  <si>
-    <t>ТМ</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Крен</t>
-  </si>
-  <si>
-    <t>Тангаж</t>
-  </si>
-  <si>
-    <t>Рысканье</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
+    </font>
+    <font>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <strike val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,40 +59,110 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -139,74 +197,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -214,7 +212,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -238,9 +236,8 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -264,44 +261,52 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw>
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw>
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw>
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -317,7 +322,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -342,60 +347,592 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625309256929" defaultRowHeight="14.3999996185303" customHeight="0" zeroHeight="0"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col width="13.1093749022008" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="14.3999996185303" customHeight="1" s="7">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>№ измерения</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>ТМ</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.3999996185303" customHeight="1" s="7">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Крен</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Тангаж</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Рысканье</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Крен</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Тангаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.3999996185303" customFormat="1" customHeight="1" s="9">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="14.3999996185303" customFormat="1" customHeight="1" s="9">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+    </row>
+    <row r="50" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+    </row>
+    <row r="52" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+    </row>
+    <row r="57" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A59" s="10" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+    </row>
+    <row r="65" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="14.3999996185303" customFormat="1" customHeight="1" s="11">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -403,6 +940,6 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.700000047683716" right="0.700000047683716" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
 </worksheet>
 </file>